--- a/EXCEL/my pratice/DASHBOARD.xlsx
+++ b/EXCEL/my pratice/DASHBOARD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\my pratice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C3453B-2DB3-4B23-BA67-89CACBBCBDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F638971-D4F1-4ADF-B551-16866E6C6D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F92601F-C931-4973-A821-D61AE66C7ECD}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -379,13 +379,13 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
@@ -926,6 +926,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -933,7 +934,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -2405,6 +2405,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2412,7 +2413,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -2897,6 +2897,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2904,7 +2905,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -3433,6 +3433,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3440,7 +3441,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -4252,6 +4252,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4259,7 +4260,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4633,6 +4633,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4640,7 +4641,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5050,6 +5050,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5057,7 +5058,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5465,6 +5465,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5472,7 +5473,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5611,7 +5611,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.7180664916885383E-2"/>
+          <c:y val="7.4801309022907894E-2"/>
+          <c:w val="0.88308311461067368"/>
+          <c:h val="0.78876434274607676"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -5808,6 +5818,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5815,7 +5826,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13526,16 +13536,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14185,7 +14195,130 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68890A53-75C9-467E-B0D1-4DFE44672DF3}" name="REGION" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8073867D-440C-4DFF-8661-E972B2E64A48}" name="PRODUCT" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="D3:E11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="7" baseField="3" baseItem="0" numFmtId="165"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{68890A53-75C9-467E-B0D1-4DFE44672DF3}" name="REGION" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -14385,8 +14518,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D97E6A3-773D-4888-8000-4899A88111DF}" name="UNITS" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D97E6A3-773D-4888-8000-4899A88111DF}" name="UNITS" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="K3:L11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -14511,8 +14644,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE108581-AEEA-492E-AA9A-9C82581C5533}" name="SALES PERSON" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE108581-AEEA-492E-AA9A-9C82581C5533}" name="SALES PERSON" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="G3:H14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -14643,129 +14776,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8073867D-440C-4DFF-8661-E972B2E64A48}" name="PRODUCT" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="D3:E11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="7" baseField="3" baseItem="0" numFmtId="165"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="3" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{467A56B6-FF21-4809-88C8-CBEC792F65DB}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="10" unboundColumnsRight="1">
@@ -14866,7 +14876,7 @@
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Sales Person" xr10:uid="{5E4B3E79-A7AD-4C93-9BD1-846D74423130}" cache="Slicer_Sales_Person" caption="Sales Person" style="SlicerStyleDark6" rowHeight="234950"/>
+  <slicer name="Sales Person" xr10:uid="{5E4B3E79-A7AD-4C93-9BD1-846D74423130}" cache="Slicer_Sales_Person" caption="Sales Person" startItem="3" style="SlicerStyleDark6" rowHeight="234950"/>
   <slicer name="Region" xr10:uid="{32551A76-2E40-4DDC-9522-D2476A353C0E}" cache="Slicer_Region" caption="Region" columnCount="2" showCaption="0" style="SlicerStyleDark6" rowHeight="234950"/>
   <slicer name="Product" xr10:uid="{FEB6FF55-854F-460B-A43D-D61E4D8C75F1}" cache="Slicer_Product" caption="Product" style="SlicerStyleDark6" rowHeight="234950"/>
 </slicers>
@@ -14881,10 +14891,10 @@
     <tableColumn id="3" xr3:uid="{6C5F8F9C-8729-41FB-9BFA-A43211CDE2B3}" uniqueName="3" name="Region" queryTableFieldId="3" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{A3273996-0295-4B44-979E-0D0FC8CB89C1}" uniqueName="4" name="Product" queryTableFieldId="4" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{CDAA8563-C708-4F1E-BB53-EC5E1D5E4B13}" uniqueName="5" name="Units Sold" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{5A5057C8-BB91-4BB7-BB50-5DD0EE11FE55}" uniqueName="6" name="Unit Price" queryTableFieldId="6" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{30DBDF02-AD1E-4880-8E7C-646EB6744EAF}" uniqueName="7" name="Cost of Goods" queryTableFieldId="7" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{4303280C-322B-4971-8FE6-32AB89C1C0F0}" uniqueName="8" name="Total Sales" queryTableFieldId="8" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{C7B12238-FAB8-446B-B5E4-ACB6E6C8AE1D}" uniqueName="9" name="profit" queryTableFieldId="9" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{5A5057C8-BB91-4BB7-BB50-5DD0EE11FE55}" uniqueName="6" name="Unit Price" queryTableFieldId="6" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{30DBDF02-AD1E-4880-8E7C-646EB6744EAF}" uniqueName="7" name="Cost of Goods" queryTableFieldId="7" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{4303280C-322B-4971-8FE6-32AB89C1C0F0}" uniqueName="8" name="Total Sales" queryTableFieldId="8" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{C7B12238-FAB8-446B-B5E4-ACB6E6C8AE1D}" uniqueName="9" name="profit" queryTableFieldId="9" dataDxfId="1">
       <calculatedColumnFormula>H2-(G2*E2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15313,7 +15323,7 @@
         <v>448000</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I51" si="0">H3-(G3*E3)</f>
+        <f>H3-(G3*E3)</f>
         <v>128000</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -15346,7 +15356,7 @@
         <v>163200</v>
       </c>
       <c r="I4" s="5">
-        <f t="shared" si="0"/>
+        <f>H4-(G4*E4)</f>
         <v>54400</v>
       </c>
       <c r="K4">
@@ -15380,7 +15390,7 @@
         <v>91000</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" si="0"/>
+        <f>H5-(G5*E5)</f>
         <v>27300</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -15413,7 +15423,7 @@
         <v>440000</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" si="0"/>
+        <f>H6-(G6*E6)</f>
         <v>110000</v>
       </c>
       <c r="K6" s="5">
@@ -15447,7 +15457,7 @@
         <v>61200</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="0"/>
+        <f>H7-(G7*E7)</f>
         <v>20400</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -15480,7 +15490,7 @@
         <v>78000</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="0"/>
+        <f>H8-(G8*E8)</f>
         <v>23400</v>
       </c>
       <c r="K8" s="2">
@@ -15514,7 +15524,7 @@
         <v>876000</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="0"/>
+        <f>H9-(G9*E9)</f>
         <v>292000</v>
       </c>
     </row>
@@ -15544,7 +15554,7 @@
         <v>60600</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="0"/>
+        <f>H10-(G10*E10)</f>
         <v>20200</v>
       </c>
     </row>
@@ -15574,7 +15584,7 @@
         <v>312000</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="0"/>
+        <f>H11-(G11*E11)</f>
         <v>104000</v>
       </c>
     </row>
@@ -15604,7 +15614,7 @@
         <v>66000</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="0"/>
+        <f>H12-(G12*E12)</f>
         <v>22000</v>
       </c>
     </row>
@@ -15634,7 +15644,7 @@
         <v>137000</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="0"/>
+        <f>H13-(G13*E13)</f>
         <v>41100</v>
       </c>
     </row>
@@ -15664,7 +15674,7 @@
         <v>336000</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="0"/>
+        <f>H14-(G14*E14)</f>
         <v>96000</v>
       </c>
     </row>
@@ -15694,7 +15704,7 @@
         <v>208000</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="0"/>
+        <f>H15-(G15*E15)</f>
         <v>52000</v>
       </c>
     </row>
@@ -15724,7 +15734,7 @@
         <v>266000</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="0"/>
+        <f>H16-(G16*E16)</f>
         <v>76000</v>
       </c>
     </row>
@@ -15754,7 +15764,7 @@
         <v>580000</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="0"/>
+        <f>H17-(G17*E17)</f>
         <v>145000</v>
       </c>
     </row>
@@ -15784,7 +15794,7 @@
         <v>49800</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="0"/>
+        <f>H18-(G18*E18)</f>
         <v>16600</v>
       </c>
     </row>
@@ -15814,7 +15824,7 @@
         <v>91000</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="0"/>
+        <f>H19-(G19*E19)</f>
         <v>27300</v>
       </c>
     </row>
@@ -15844,7 +15854,7 @@
         <v>1080000</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="0"/>
+        <f>H20-(G20*E20)</f>
         <v>324000</v>
       </c>
     </row>
@@ -15874,7 +15884,7 @@
         <v>576000</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="0"/>
+        <f>H21-(G21*E21)</f>
         <v>144000</v>
       </c>
     </row>
@@ -15904,7 +15914,7 @@
         <v>55200</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="0"/>
+        <f>H22-(G22*E22)</f>
         <v>18400</v>
       </c>
     </row>
@@ -15934,7 +15944,7 @@
         <v>426000</v>
       </c>
       <c r="I23" s="5">
-        <f t="shared" si="0"/>
+        <f>H23-(G23*E23)</f>
         <v>142000</v>
       </c>
     </row>
@@ -15964,7 +15974,7 @@
         <v>61800</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="0"/>
+        <f>H24-(G24*E24)</f>
         <v>20600</v>
       </c>
     </row>
@@ -15994,7 +16004,7 @@
         <v>55000</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="0"/>
+        <f>H25-(G25*E25)</f>
         <v>16500</v>
       </c>
     </row>
@@ -16024,7 +16034,7 @@
         <v>372000</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="0"/>
+        <f>H26-(G26*E26)</f>
         <v>93000</v>
       </c>
     </row>
@@ -16054,7 +16064,7 @@
         <v>85800</v>
       </c>
       <c r="I27" s="5">
-        <f t="shared" si="0"/>
+        <f>H27-(G27*E27)</f>
         <v>28600</v>
       </c>
     </row>
@@ -16084,7 +16094,7 @@
         <v>500500</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="0"/>
+        <f>H28-(G28*E28)</f>
         <v>143000</v>
       </c>
     </row>
@@ -16114,7 +16124,7 @@
         <v>59400</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="0"/>
+        <f>H29-(G29*E29)</f>
         <v>19800</v>
       </c>
     </row>
@@ -16144,7 +16154,7 @@
         <v>120000</v>
       </c>
       <c r="I30" s="5">
-        <f t="shared" si="0"/>
+        <f>H30-(G30*E30)</f>
         <v>36000</v>
       </c>
     </row>
@@ -16174,7 +16184,7 @@
         <v>231000</v>
       </c>
       <c r="I31" s="5">
-        <f t="shared" si="0"/>
+        <f>H31-(G31*E31)</f>
         <v>66000</v>
       </c>
     </row>
@@ -16204,7 +16214,7 @@
         <v>105600</v>
       </c>
       <c r="I32" s="5">
-        <f t="shared" si="0"/>
+        <f>H32-(G32*E32)</f>
         <v>35200</v>
       </c>
     </row>
@@ -16234,7 +16244,7 @@
         <v>1270000</v>
       </c>
       <c r="I33" s="5">
-        <f t="shared" si="0"/>
+        <f>H33-(G33*E33)</f>
         <v>381000</v>
       </c>
     </row>
@@ -16264,7 +16274,7 @@
         <v>268000</v>
       </c>
       <c r="I34" s="5">
-        <f t="shared" si="0"/>
+        <f>H34-(G34*E34)</f>
         <v>67000</v>
       </c>
     </row>
@@ -16294,7 +16304,7 @@
         <v>80400</v>
       </c>
       <c r="I35" s="5">
-        <f t="shared" si="0"/>
+        <f>H35-(G35*E35)</f>
         <v>26800</v>
       </c>
     </row>
@@ -16324,7 +16334,7 @@
         <v>149000</v>
       </c>
       <c r="I36" s="5">
-        <f t="shared" si="0"/>
+        <f>H36-(G36*E36)</f>
         <v>44700</v>
       </c>
     </row>
@@ -16354,7 +16364,7 @@
         <v>62400</v>
       </c>
       <c r="I37" s="5">
-        <f t="shared" si="0"/>
+        <f>H37-(G37*E37)</f>
         <v>20800</v>
       </c>
     </row>
@@ -16384,7 +16394,7 @@
         <v>34200</v>
       </c>
       <c r="I38" s="5">
-        <f t="shared" si="0"/>
+        <f>H38-(G38*E38)</f>
         <v>11400</v>
       </c>
     </row>
@@ -16414,7 +16424,7 @@
         <v>54000</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" si="0"/>
+        <f>H39-(G39*E39)</f>
         <v>18000</v>
       </c>
     </row>
@@ -16444,7 +16454,7 @@
         <v>40200</v>
       </c>
       <c r="I40" s="5">
-        <f t="shared" si="0"/>
+        <f>H40-(G40*E40)</f>
         <v>13400</v>
       </c>
     </row>
@@ -16474,7 +16484,7 @@
         <v>508000</v>
       </c>
       <c r="I41" s="5">
-        <f t="shared" si="0"/>
+        <f>H41-(G41*E41)</f>
         <v>127000</v>
       </c>
     </row>
@@ -16504,7 +16514,7 @@
         <v>108000</v>
       </c>
       <c r="I42" s="5">
-        <f t="shared" si="0"/>
+        <f>H42-(G42*E42)</f>
         <v>32400</v>
       </c>
     </row>
@@ -16534,7 +16544,7 @@
         <v>231000</v>
       </c>
       <c r="I43" s="5">
-        <f t="shared" si="0"/>
+        <f>H43-(G43*E43)</f>
         <v>66000</v>
       </c>
     </row>
@@ -16564,7 +16574,7 @@
         <v>468000</v>
       </c>
       <c r="I44" s="5">
-        <f t="shared" si="0"/>
+        <f>H44-(G44*E44)</f>
         <v>156000</v>
       </c>
     </row>
@@ -16594,7 +16604,7 @@
         <v>69000</v>
       </c>
       <c r="I45" s="5">
-        <f t="shared" si="0"/>
+        <f>H45-(G45*E45)</f>
         <v>20700</v>
       </c>
     </row>
@@ -16624,7 +16634,7 @@
         <v>70800</v>
       </c>
       <c r="I46" s="5">
-        <f t="shared" si="0"/>
+        <f>H46-(G46*E46)</f>
         <v>23600</v>
       </c>
     </row>
@@ -16654,7 +16664,7 @@
         <v>65400</v>
       </c>
       <c r="I47" s="5">
-        <f t="shared" si="0"/>
+        <f>H47-(G47*E47)</f>
         <v>21800</v>
       </c>
     </row>
@@ -16684,7 +16694,7 @@
         <v>244000</v>
       </c>
       <c r="I48" s="5">
-        <f t="shared" si="0"/>
+        <f>H48-(G48*E48)</f>
         <v>61000</v>
       </c>
     </row>
@@ -16714,7 +16724,7 @@
         <v>78000</v>
       </c>
       <c r="I49" s="5">
-        <f t="shared" si="0"/>
+        <f>H49-(G49*E49)</f>
         <v>26000</v>
       </c>
     </row>
@@ -16744,7 +16754,7 @@
         <v>210000</v>
       </c>
       <c r="I50" s="5">
-        <f t="shared" si="0"/>
+        <f>H50-(G50*E50)</f>
         <v>60000</v>
       </c>
     </row>
@@ -16774,7 +16784,7 @@
         <v>438000</v>
       </c>
       <c r="I51" s="5">
-        <f t="shared" si="0"/>
+        <f>H51-(G51*E51)</f>
         <v>146000</v>
       </c>
     </row>

--- a/EXCEL/my pratice/DASHBOARD.xlsx
+++ b/EXCEL/my pratice/DASHBOARD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\my pratice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F638971-D4F1-4ADF-B551-16866E6C6D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E67FA3-B732-4FCE-B87B-B2BC27F40E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3F92601F-C931-4973-A821-D61AE66C7ECD}"/>
   </bookViews>
@@ -379,13 +379,13 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ ##\.##,&quot;L&quot;"/>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
@@ -5810,7 +5810,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -13536,15 +13536,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>990600</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -14891,10 +14891,10 @@
     <tableColumn id="3" xr3:uid="{6C5F8F9C-8729-41FB-9BFA-A43211CDE2B3}" uniqueName="3" name="Region" queryTableFieldId="3" dataDxfId="5"/>
     <tableColumn id="4" xr3:uid="{A3273996-0295-4B44-979E-0D0FC8CB89C1}" uniqueName="4" name="Product" queryTableFieldId="4" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{CDAA8563-C708-4F1E-BB53-EC5E1D5E4B13}" uniqueName="5" name="Units Sold" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{5A5057C8-BB91-4BB7-BB50-5DD0EE11FE55}" uniqueName="6" name="Unit Price" queryTableFieldId="6" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{30DBDF02-AD1E-4880-8E7C-646EB6744EAF}" uniqueName="7" name="Cost of Goods" queryTableFieldId="7" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{4303280C-322B-4971-8FE6-32AB89C1C0F0}" uniqueName="8" name="Total Sales" queryTableFieldId="8" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{C7B12238-FAB8-446B-B5E4-ACB6E6C8AE1D}" uniqueName="9" name="profit" queryTableFieldId="9" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{5A5057C8-BB91-4BB7-BB50-5DD0EE11FE55}" uniqueName="6" name="Unit Price" queryTableFieldId="6" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{30DBDF02-AD1E-4880-8E7C-646EB6744EAF}" uniqueName="7" name="Cost of Goods" queryTableFieldId="7" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{4303280C-322B-4971-8FE6-32AB89C1C0F0}" uniqueName="8" name="Total Sales" queryTableFieldId="8" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{C7B12238-FAB8-446B-B5E4-ACB6E6C8AE1D}" uniqueName="9" name="profit" queryTableFieldId="9" dataDxfId="0">
       <calculatedColumnFormula>H2-(G2*E2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15289,7 +15289,7 @@
         <v>504000</v>
       </c>
       <c r="I2" s="5">
-        <f>H2-(G2*E2)</f>
+        <f t="shared" ref="I2:I33" si="0">H2-(G2*E2)</f>
         <v>168000</v>
       </c>
       <c r="K2" s="2">
@@ -15323,7 +15323,7 @@
         <v>448000</v>
       </c>
       <c r="I3" s="5">
-        <f>H3-(G3*E3)</f>
+        <f t="shared" si="0"/>
         <v>128000</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -15356,7 +15356,7 @@
         <v>163200</v>
       </c>
       <c r="I4" s="5">
-        <f>H4-(G4*E4)</f>
+        <f t="shared" si="0"/>
         <v>54400</v>
       </c>
       <c r="K4">
@@ -15390,7 +15390,7 @@
         <v>91000</v>
       </c>
       <c r="I5" s="5">
-        <f>H5-(G5*E5)</f>
+        <f t="shared" si="0"/>
         <v>27300</v>
       </c>
       <c r="K5" s="1" t="s">
@@ -15423,7 +15423,7 @@
         <v>440000</v>
       </c>
       <c r="I6" s="5">
-        <f>H6-(G6*E6)</f>
+        <f t="shared" si="0"/>
         <v>110000</v>
       </c>
       <c r="K6" s="5">
@@ -15457,7 +15457,7 @@
         <v>61200</v>
       </c>
       <c r="I7" s="5">
-        <f>H7-(G7*E7)</f>
+        <f t="shared" si="0"/>
         <v>20400</v>
       </c>
       <c r="K7" s="1" t="s">
@@ -15490,7 +15490,7 @@
         <v>78000</v>
       </c>
       <c r="I8" s="5">
-        <f>H8-(G8*E8)</f>
+        <f t="shared" si="0"/>
         <v>23400</v>
       </c>
       <c r="K8" s="2">
@@ -15524,7 +15524,7 @@
         <v>876000</v>
       </c>
       <c r="I9" s="5">
-        <f>H9-(G9*E9)</f>
+        <f t="shared" si="0"/>
         <v>292000</v>
       </c>
     </row>
@@ -15554,7 +15554,7 @@
         <v>60600</v>
       </c>
       <c r="I10" s="5">
-        <f>H10-(G10*E10)</f>
+        <f t="shared" si="0"/>
         <v>20200</v>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
         <v>312000</v>
       </c>
       <c r="I11" s="5">
-        <f>H11-(G11*E11)</f>
+        <f t="shared" si="0"/>
         <v>104000</v>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
         <v>66000</v>
       </c>
       <c r="I12" s="5">
-        <f>H12-(G12*E12)</f>
+        <f t="shared" si="0"/>
         <v>22000</v>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
         <v>137000</v>
       </c>
       <c r="I13" s="5">
-        <f>H13-(G13*E13)</f>
+        <f t="shared" si="0"/>
         <v>41100</v>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
         <v>336000</v>
       </c>
       <c r="I14" s="5">
-        <f>H14-(G14*E14)</f>
+        <f t="shared" si="0"/>
         <v>96000</v>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
         <v>208000</v>
       </c>
       <c r="I15" s="5">
-        <f>H15-(G15*E15)</f>
+        <f t="shared" si="0"/>
         <v>52000</v>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
         <v>266000</v>
       </c>
       <c r="I16" s="5">
-        <f>H16-(G16*E16)</f>
+        <f t="shared" si="0"/>
         <v>76000</v>
       </c>
     </row>
@@ -15764,7 +15764,7 @@
         <v>580000</v>
       </c>
       <c r="I17" s="5">
-        <f>H17-(G17*E17)</f>
+        <f t="shared" si="0"/>
         <v>145000</v>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
         <v>49800</v>
       </c>
       <c r="I18" s="5">
-        <f>H18-(G18*E18)</f>
+        <f t="shared" si="0"/>
         <v>16600</v>
       </c>
     </row>
@@ -15824,7 +15824,7 @@
         <v>91000</v>
       </c>
       <c r="I19" s="5">
-        <f>H19-(G19*E19)</f>
+        <f t="shared" si="0"/>
         <v>27300</v>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
         <v>1080000</v>
       </c>
       <c r="I20" s="5">
-        <f>H20-(G20*E20)</f>
+        <f t="shared" si="0"/>
         <v>324000</v>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
         <v>576000</v>
       </c>
       <c r="I21" s="5">
-        <f>H21-(G21*E21)</f>
+        <f t="shared" si="0"/>
         <v>144000</v>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
         <v>55200</v>
       </c>
       <c r="I22" s="5">
-        <f>H22-(G22*E22)</f>
+        <f t="shared" si="0"/>
         <v>18400</v>
       </c>
     </row>
@@ -15944,7 +15944,7 @@
         <v>426000</v>
       </c>
       <c r="I23" s="5">
-        <f>H23-(G23*E23)</f>
+        <f t="shared" si="0"/>
         <v>142000</v>
       </c>
     </row>
@@ -15974,7 +15974,7 @@
         <v>61800</v>
       </c>
       <c r="I24" s="5">
-        <f>H24-(G24*E24)</f>
+        <f t="shared" si="0"/>
         <v>20600</v>
       </c>
     </row>
@@ -16004,7 +16004,7 @@
         <v>55000</v>
       </c>
       <c r="I25" s="5">
-        <f>H25-(G25*E25)</f>
+        <f t="shared" si="0"/>
         <v>16500</v>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
         <v>372000</v>
       </c>
       <c r="I26" s="5">
-        <f>H26-(G26*E26)</f>
+        <f t="shared" si="0"/>
         <v>93000</v>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
         <v>85800</v>
       </c>
       <c r="I27" s="5">
-        <f>H27-(G27*E27)</f>
+        <f t="shared" si="0"/>
         <v>28600</v>
       </c>
     </row>
@@ -16094,7 +16094,7 @@
         <v>500500</v>
       </c>
       <c r="I28" s="5">
-        <f>H28-(G28*E28)</f>
+        <f t="shared" si="0"/>
         <v>143000</v>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
         <v>59400</v>
       </c>
       <c r="I29" s="5">
-        <f>H29-(G29*E29)</f>
+        <f t="shared" si="0"/>
         <v>19800</v>
       </c>
     </row>
@@ -16154,7 +16154,7 @@
         <v>120000</v>
       </c>
       <c r="I30" s="5">
-        <f>H30-(G30*E30)</f>
+        <f t="shared" si="0"/>
         <v>36000</v>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
         <v>231000</v>
       </c>
       <c r="I31" s="5">
-        <f>H31-(G31*E31)</f>
+        <f t="shared" si="0"/>
         <v>66000</v>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v>105600</v>
       </c>
       <c r="I32" s="5">
-        <f>H32-(G32*E32)</f>
+        <f t="shared" si="0"/>
         <v>35200</v>
       </c>
     </row>
@@ -16244,7 +16244,7 @@
         <v>1270000</v>
       </c>
       <c r="I33" s="5">
-        <f>H33-(G33*E33)</f>
+        <f t="shared" si="0"/>
         <v>381000</v>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
         <v>268000</v>
       </c>
       <c r="I34" s="5">
-        <f>H34-(G34*E34)</f>
+        <f t="shared" ref="I34:I65" si="1">H34-(G34*E34)</f>
         <v>67000</v>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
         <v>80400</v>
       </c>
       <c r="I35" s="5">
-        <f>H35-(G35*E35)</f>
+        <f t="shared" si="1"/>
         <v>26800</v>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
         <v>149000</v>
       </c>
       <c r="I36" s="5">
-        <f>H36-(G36*E36)</f>
+        <f t="shared" si="1"/>
         <v>44700</v>
       </c>
     </row>
@@ -16364,7 +16364,7 @@
         <v>62400</v>
       </c>
       <c r="I37" s="5">
-        <f>H37-(G37*E37)</f>
+        <f t="shared" si="1"/>
         <v>20800</v>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
         <v>34200</v>
       </c>
       <c r="I38" s="5">
-        <f>H38-(G38*E38)</f>
+        <f t="shared" si="1"/>
         <v>11400</v>
       </c>
     </row>
@@ -16424,7 +16424,7 @@
         <v>54000</v>
       </c>
       <c r="I39" s="5">
-        <f>H39-(G39*E39)</f>
+        <f t="shared" si="1"/>
         <v>18000</v>
       </c>
     </row>
@@ -16454,7 +16454,7 @@
         <v>40200</v>
       </c>
       <c r="I40" s="5">
-        <f>H40-(G40*E40)</f>
+        <f t="shared" si="1"/>
         <v>13400</v>
       </c>
     </row>
@@ -16484,7 +16484,7 @@
         <v>508000</v>
       </c>
       <c r="I41" s="5">
-        <f>H41-(G41*E41)</f>
+        <f t="shared" si="1"/>
         <v>127000</v>
       </c>
     </row>
@@ -16514,7 +16514,7 @@
         <v>108000</v>
       </c>
       <c r="I42" s="5">
-        <f>H42-(G42*E42)</f>
+        <f t="shared" si="1"/>
         <v>32400</v>
       </c>
     </row>
@@ -16544,7 +16544,7 @@
         <v>231000</v>
       </c>
       <c r="I43" s="5">
-        <f>H43-(G43*E43)</f>
+        <f t="shared" si="1"/>
         <v>66000</v>
       </c>
     </row>
@@ -16574,7 +16574,7 @@
         <v>468000</v>
       </c>
       <c r="I44" s="5">
-        <f>H44-(G44*E44)</f>
+        <f t="shared" si="1"/>
         <v>156000</v>
       </c>
     </row>
@@ -16604,7 +16604,7 @@
         <v>69000</v>
       </c>
       <c r="I45" s="5">
-        <f>H45-(G45*E45)</f>
+        <f t="shared" si="1"/>
         <v>20700</v>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
         <v>70800</v>
       </c>
       <c r="I46" s="5">
-        <f>H46-(G46*E46)</f>
+        <f t="shared" si="1"/>
         <v>23600</v>
       </c>
     </row>
@@ -16664,7 +16664,7 @@
         <v>65400</v>
       </c>
       <c r="I47" s="5">
-        <f>H47-(G47*E47)</f>
+        <f t="shared" si="1"/>
         <v>21800</v>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
         <v>244000</v>
       </c>
       <c r="I48" s="5">
-        <f>H48-(G48*E48)</f>
+        <f t="shared" si="1"/>
         <v>61000</v>
       </c>
     </row>
@@ -16724,7 +16724,7 @@
         <v>78000</v>
       </c>
       <c r="I49" s="5">
-        <f>H49-(G49*E49)</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
         <v>210000</v>
       </c>
       <c r="I50" s="5">
-        <f>H50-(G50*E50)</f>
+        <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
         <v>438000</v>
       </c>
       <c r="I51" s="5">
-        <f>H51-(G51*E51)</f>
+        <f t="shared" si="1"/>
         <v>146000</v>
       </c>
     </row>
